--- a/excel_file.xlsx
+++ b/excel_file.xlsx
@@ -425,63 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scenario ID</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Scenario Title</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Test Case Title</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Preconditions</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test Type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Feasible</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Step #</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Test Step Description</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -493,1602 +468,1275 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>US32275</t>
+          <t>US32275 - Verify side-by-side plan comparison</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plan Recommendation</t>
+          <t>1. Navigate to plan recommendation page 2. Review side-by-side displayed plans</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Verify side-by-side plan comparison</t>
+          <t>System displays at least two plans side-by-side with premiums, deductibles, co-pays, out-of-pocket maximums, and coverage for specified medications and doctors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>User is logged into the CareSource enrollment portal and has completed the health needs questionnaire</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>User with completed profile and at least two recommended plans</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Navigate to plan recommendation page</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>System displays side-by-side comparison of at least two plans highlighting premiums, deductibles, co-pays, out-of-pocket maximums, and coverage for specified medications and doctors</t>
+          <t>Derived from provided scenario; no direct PII/PHI/PCI included</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Review plan features and select a plan</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Selected plan is highlighted and user can proceed to enrollment</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>US32275 - Select plan and proceed to enrollment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1. Review plan features 2. Select a plan 3. Click proceed/enroll</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Selected plan is highlighted and user can continue to enrollment</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Functional happy path</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC002</t>
+          <t>TC003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>US32275</t>
+          <t>US32275 - Verify navigation to enrollment after plan selection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plan Recommendation</t>
+          <t>1. On comparison page select a plan 2. Click Enroll</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Verify navigation to enrollment after plan selection</t>
+          <t>System transitions to enrollment with chosen plan pre-selected</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>User is on the plan comparison page</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>User with at least one recommended plan</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Select a plan and click 'Enroll'</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>System transitions to the enrollment process with the chosen plan pre-selected</t>
+          <t>Functional navigation validation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC003</t>
+          <t>TC004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>US32275</t>
+          <t>US32275 - No recommended plans available</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plan Recommendation</t>
+          <t>1. Navigate to plan recommendation page with criteria yielding no matches</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Negative - No recommended plans</t>
+          <t>System displays message indicating no plans match criteria and prompts user to adjust preferences</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>User has completed health needs but no plans match criteria</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>User with uncommon criteria resulting in no matches</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Navigate to plan recommendation page</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>System displays a message: "No plans match your criteria. Please adjust your preferences."</t>
+          <t>Negative scenario</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC004</t>
+          <t>TC005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>US32275</t>
+          <t>US32275 - Maximum number of recommended plans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plan Recommendation</t>
+          <t>1. Navigate to recommendation page with broad criteria 2. Scroll through results</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Edge - Maximum number of plans</t>
+          <t>System displays all recommended plans in a readable scrollable format without UI breakage</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>User qualifies for 10+ plans</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>User with broad criteria resulting in maximum recommendations</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Navigate to plan recommendation page</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>System displays all recommended plans in a scrollable, readable format without UI breakage</t>
+          <t>Edge/UI resiliency</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC005</t>
+          <t>TC006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>US32274</t>
+          <t>US32275 - Comparison page loads with minimum required data</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plan Personalization</t>
+          <t>1. Navigate to recommendation page after questionnaire completion</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Verify member can input medications and providers</t>
+          <t>System loads comparison page successfully with required plan data fields populated</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>User is authenticated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Medication: Metformin 500mg, Provider: Dr. Smith</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Navigate to health needs input page</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>System displays input fields for medications and providers</t>
+          <t>Acceptance coverage extension</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Enter medication and provider information and submit</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>System accepts input, validates data, and confirms successful entry</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>US32274 - Input medications and providers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. Navigate to health needs input page 2. Enter medication and provider information 3. Submit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>System displays input fields, accepts valid entries, validates data, and confirms successful entry</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Uses non-identifying sample data only</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC006</t>
+          <t>TC008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>US32274</t>
+          <t>US32274 - Input financial preferences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plan Personalization</t>
+          <t>1. Navigate to financial preferences section 2. Enter premium, deductible, and out-of-pocket maximum 3. Submit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Verify financial preference input</t>
+          <t>System saves preferences and updates recommendation criteria</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>User is authenticated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Premium: $200, Deductible: $1000, OOP Max: $5000</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Navigate to financial preferences section</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>System displays fields for premium, deductible, and out-of-pocket maximum</t>
+          <t>Functional scenario</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Enter preferences and submit</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>System saves preferences and updates recommendation criteria</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>US32274 - Blank medication entry validation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1. Leave medication field blank 2. Submit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>System displays validation error indicating medication name is required</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Negative validation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC007</t>
+          <t>TC010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>US32274</t>
+          <t>US32274 - Large medication list processing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plan Personalization</t>
+          <t>1. Enter 20 or more medications 2. Submit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Negative - Invalid medication entry</t>
+          <t>System accepts all entries and processes recommendations without error</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>User is authenticated</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Medication: "" (blank entry)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Leave medication field blank and submit</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>System displays error: "Medication name required"</t>
+          <t>Edge volume scenario</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TC008</t>
+          <t>TC011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>US32274</t>
+          <t>US32274 - Invalid provider format handling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plan Personalization</t>
+          <t>1. Enter unsupported characters or malformed provider text 2. Submit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Edge - Large medication list</t>
+          <t>System validates input and displays appropriate error or sanitizes content per rules</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>User is authenticated</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Medication: 20+ entries</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Enter 20+ medications and submit</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>System accepts all entries and processes recommendations without error</t>
+          <t>Added edge validation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TC009</t>
+          <t>TC012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>US32273</t>
+          <t>US32274 - Boundary financial preference values</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Guided Enrollment</t>
+          <t>1. Enter minimum and maximum allowed financial values 2. Submit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Verify guided workflow for plan selection</t>
+          <t>System accepts in-range values and rejects out-of-range values with clear validation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>User is a prospective member</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Health: Asthma, PCP: Dr. Lee, Premium: $150</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Start guided enrollment</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>System prompts for health data, provider, and financial preferences in sequence</t>
+          <t>Boundary coverage</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Complete all steps and submit</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>System generates and displays personalized plan recommendations with comparison tool</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>US32273 - Guided workflow prompts in sequence</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1. Start guided enrollment</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>System prompts for health data, provider, and financial preferences in the expected sequence</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Functional guided flow</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC010</t>
+          <t>TC014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>US32273</t>
+          <t>US32273 - Complete guided enrollment and receive recommendations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Guided Enrollment</t>
+          <t>1. Start guided enrollment 2. Complete all required steps 3. Submit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Negative - Missing required fields</t>
+          <t>System generates and displays personalized plan recommendations with comparison tool</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>User is a prospective member</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Omit required health data</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Attempt to proceed without entering all required fields</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>System displays validation errors for missing fields</t>
+          <t>End-to-end functional coverage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC011</t>
+          <t>TC015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>US32273</t>
+          <t>US32273 - Missing required fields in guided enrollment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Guided Enrollment</t>
+          <t>1. Attempt to proceed without entering all required fields</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Edge - Extreme cost preferences</t>
+          <t>System displays validation errors for missing required fields</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>User is a prospective member</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Premium: $0, Deductible: $0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Enter extreme values and submit</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>System processes and displays only plans meeting criteria, or a message if none available</t>
+          <t>Negative validation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC012</t>
+          <t>TC016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>US31822</t>
+          <t>US32273 - Extreme cost preferences</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Demographic Input</t>
+          <t>1. Enter extreme values such as zero premium and zero deductible 2. Submit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Verify demographic and health needs input</t>
+          <t>System processes criteria and displays matching plans or an informative no-plan message</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>User is a prospective member</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Age: 40, Location: OH, Doctor: Dr. Adams, Medication: Lisinopril</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Navigate to demographic input page</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>System displays fields for age, location, doctors, medications</t>
+          <t>Edge scenario</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Enter data and submit</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>System validates and accepts input, proceeding to recommendations</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>US32273 - Back and next navigation retains data</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1. Enter data in guided steps 2. Navigate back and forward between steps</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Previously entered data remains available and accurate</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Usability/data retention</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC013</t>
+          <t>TC018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>US31822</t>
+          <t>US31822 - Enter demographic and health needs data</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Demographic Input</t>
+          <t>1. Navigate to demographic input page 2. Enter age, location, doctors, and medications 3. Submit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Negative - Invalid age</t>
+          <t>System validates and accepts input, then proceeds to recommendations</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>User is a prospective member</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Age: -1</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Enter invalid age and submit</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>System displays error: "Invalid age"</t>
+          <t>Functional scenario</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC014</t>
+          <t>TC019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>US31822</t>
+          <t>US31822 - Invalid age validation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Demographic Input</t>
+          <t>1. Enter invalid age such as negative value 2. Submit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Edge - Maximum field length</t>
+          <t>System displays invalid age error</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>User is a prospective member</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Doctor name: 100+ characters</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Enter maximum length for doctor name and submit</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>System accepts or displays appropriate error without crashing</t>
+          <t>Negative validation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC015</t>
+          <t>TC020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>US32306</t>
+          <t>US31822 - Maximum field length for doctor name</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>1. Enter doctor name at maximum supported length or above 2. Submit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Verify profile view</t>
+          <t>System accepts valid maximum length or displays appropriate validation without crashing</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>User with profile data</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Navigate to profile page</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>System displays correct profile information</t>
+          <t>Edge robustness</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC016</t>
+          <t>TC021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>US32307</t>
+          <t>US31822 - Required demographic fields missing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>1. Leave one or more required demographic fields blank 2. Submit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Verify settings update</t>
+          <t>System highlights missing required fields and prevents continuation</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>New notification preference</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Go to settings, change preference, save</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>System updates and confirms setting change</t>
+          <t>Added acceptance coverage</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC017</t>
+          <t>TC022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>US32308</t>
+          <t>US32306 - View profile information</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Transaction History</t>
+          <t>1. Navigate to profile page</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Verify transaction history view</t>
+          <t>System displays correct profile information for logged-in user</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>User with transaction history</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Navigate to transaction history</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>System displays all past transactions</t>
+          <t>Functional smoke</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TC018</t>
+          <t>TC023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>US32309</t>
+          <t>US32307 - Update settings</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Search and Filter</t>
+          <t>1. Go to settings 2. Change preference 3. Save</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Verify data search and filter</t>
+          <t>System updates setting and confirms change</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Search: "Diabetes", Filter: Date range</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Enter search term and filter</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>System returns correct filtered data</t>
+          <t>Functional smoke</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TC019</t>
+          <t>TC024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>US32310</t>
+          <t>US32308 - View transaction history</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Export Reports</t>
+          <t>1. Navigate to transaction history</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Verify report export</t>
+          <t>System displays all available past transactions for user</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Report: Claims</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Click export on claims report</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>System downloads report in selected format</t>
+          <t>Functional smoke</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TC020</t>
+          <t>TC025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>US32311</t>
+          <t>US32309 - Search and filter data</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>User Permissions</t>
+          <t>1. Enter search term 2. Apply date range filter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Verify permission management</t>
+          <t>System returns correct filtered data</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Admin user logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Assign 'Editor' to user X</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Navigate to permissions, assign role</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>System saves and reflects new permission</t>
+          <t>Functional search/filter</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TC021</t>
+          <t>TC026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>US32312</t>
+          <t>US32310 - Export reports</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>System Logs</t>
+          <t>1. Click export on target report</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Verify system log view</t>
+          <t>System downloads report in selected format</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Admin user logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Any log record</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Navigate to system logs</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>System displays logs with timestamp, user, action</t>
+          <t>Functional export</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TC022</t>
+          <t>TC027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US32304</t>
+          <t>US32311 - Manage user permissions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Password Reset</t>
+          <t>1. Navigate to permissions 2. Assign role to target user 3. Save</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Verify password reset</t>
+          <t>System saves and reflects new permission</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>User on login page</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Registered email</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Click 'Forgot Password', enter email</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>System sends reset link to email</t>
+          <t>Admin functional scenario</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TC023</t>
+          <t>TC028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US32305</t>
+          <t>US32312 - View system logs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Two-Factor Authentication</t>
+          <t>1. Navigate to system logs</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Verify 2FA enablement</t>
+          <t>System displays logs including timestamp, user, and action</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Valid phone number</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Navigate to security, enable 2FA</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>System sends code and confirms setup</t>
+          <t>Admin observability</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TC024</t>
+          <t>TC029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US32303</t>
+          <t>US32304 - Password reset request</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>1. Click Forgot Password 2. Enter registered email 3. Submit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Verify email login</t>
+          <t>System sends reset link or reset instructions to registered email</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>User is registered</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Valid email/password</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Enter credentials, click login</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>System authenticates and redirects to dashboard</t>
+          <t>Authentication support flow</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TC025</t>
+          <t>TC030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>US32983</t>
+          <t>US32305 - Enable two-factor authentication</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEW STORY TETS</t>
+          <t>1. Navigate to security settings 2. Enable 2FA 3. Enter valid phone number 4. Confirm code</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Basic smoke test</t>
+          <t>System sends verification code and confirms 2FA setup</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>System available</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Access feature</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Feature loads without error</t>
+          <t>Security feature</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TC026</t>
+          <t>TC031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>US32744</t>
+          <t>US32303 - Valid email login</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>member 1</t>
+          <t>1. Enter valid email and password 2. Click login</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Basic smoke test</t>
+          <t>System authenticates user and redirects to dashboard</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>System available</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Access feature</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>Core authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>US32303 - Invalid email login</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1. Enter invalid credentials 2. Click login</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>System denies access and displays appropriate error message</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Added negative coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>US32303 - Account lock after repeated failed logins</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1. Attempt login with invalid credentials five times or per configured threshold</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>System locks account or triggers configured protection mechanism after threshold is reached</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Security edge aligned to sample acceptance pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>US32983 - New story basic smoke test</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1. Access feature</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Feature loads without error</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Smoke coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>US32744 - Member 1 basic smoke test</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1. Access feature</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Smoke coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cross-story compliance - Verify no sensitive data exposed in UI messages</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1. Execute representative negative and functional scenarios 2. Review UI messages and logs visible to user</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>System does not expose sensitive personal, health, or payment data in user-visible messages</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Compliance review case</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cross-story accessibility - Keyboard navigation on major workflows</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1. Navigate major workflows using keyboard only</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Interactive elements are reachable and usable via keyboard navigation</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Added quality edge case</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cross-story session handling - Session timeout during workflow</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1. Start workflow 2. Allow session to expire 3. Attempt next action</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>System redirects user appropriately and preserves or safely discards data per requirements</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Security/usability edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cross-story performance - Recommendation page load under expected volume</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1. Load recommendation page with standard dataset</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Page loads within acceptable response time and remains usable</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Non-functional performance check</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cross-story error handling - Backend/service unavailable</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1. Attempt feature action while dependent service is unavailable</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>System shows user-friendly error message and does not crash</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Resilience scenario</t>
         </is>
       </c>
     </row>
